--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI - Copia.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI - Copia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11805141-273B-4B99-B1A4-5298099B4F93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F93D7608-6AE3-4DAA-924F-AEBAD7A580A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -441,7 +441,7 @@
     <t>135832425</t>
   </si>
   <si>
-    <t xml:space="preserve">Indexação FG Sicred 23.12 </t>
+    <t>Relatório Recusa _ SICREDI_23.12.2025</t>
   </si>
 </sst>
 </file>
@@ -3136,31 +3136,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>